--- a/data/trans_orig/P33_1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33_1_2023-Habitat-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de horas que duerme habitualmente al día entre semana</t>
+          <t>Número medio de horas que duerme habitualmente al día entre semana (tasa de respuesta: 97,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -576,12 +576,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,84; 6,99</t>
+          <t>6,84; 7,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,09</t>
+          <t>6,98; 7,11</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,19; 7,67</t>
+          <t>7,19; 7,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,13; 7,49</t>
+          <t>7,12; 7,49</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,01; 7,21</t>
+          <t>7,01; 7,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,39; 7,07</t>
+          <t>6,45; 7,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,61; 7,09</t>
+          <t>6,57; 7,1</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,92; 7,09</t>
+          <t>6,93; 7,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,91; 7,03</t>
+          <t>6,9; 7,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,93; 7,03</t>
+          <t>6,94; 7,04</t>
         </is>
       </c>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,77; 7,01</t>
+          <t>6,75; 7,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,14</t>
+          <t>6,97; 7,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33_1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33_1_2023-Habitat-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>7,16</t>
+          <t>7,15</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6,91</t>
+          <t>6,92</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,04</t>
+          <t>7,03</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,07; 7,26</t>
+          <t>7,06; 7,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,11</t>
+          <t>6,97; 7,09</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,37</t>
+          <t>7,23</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,07</t>
+          <t>7,1</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,24</t>
+          <t>7,16</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,19; 7,71</t>
+          <t>7,16; 7,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,01; 7,14</t>
+          <t>7,03; 7,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,12; 7,49</t>
+          <t>7,12; 7,21</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7,11</t>
+          <t>7,12</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,8</t>
+          <t>7,04</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,93</t>
+          <t>7,08</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,01; 7,22</t>
+          <t>7,02; 7,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,45; 7,06</t>
+          <t>6,96; 7,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,57; 7,1</t>
+          <t>7,02; 7,14</t>
         </is>
       </c>
     </row>
@@ -698,12 +698,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7,01</t>
+          <t>7,02</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,96</t>
+          <t>6,95</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,93; 7,1</t>
+          <t>6,94; 7,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,9; 7,02</t>
+          <t>6,88; 7,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,94; 7,04</t>
+          <t>6,93; 7,03</t>
         </is>
       </c>
     </row>
@@ -748,12 +748,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7,18</t>
+          <t>7,13</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,94</t>
+          <t>7,01</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,1; 7,37</t>
+          <t>7,09; 7,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,75; 7,01</t>
+          <t>6,97; 7,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,15</t>
+          <t>7,04; 7,09</t>
         </is>
       </c>
     </row>
